--- a/sample/expected-output-mixed.xlsx
+++ b/sample/expected-output-mixed.xlsx
@@ -434,107 +434,107 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>next step</t>
+          <t>actions</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30010482731</t>
+          <t>30040995108</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18 Wte 600x900 CAD-104827</t>
+          <t>18 Anth 651x824 CAD-409951</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Finished, no action</t>
+          <t>117 to Drill</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>30040995108</t>
+          <t>30026196225</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18 Anth 651x824 CAD-409951</t>
+          <t>18 Oak 662x854 CAD-261962</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>117</v>
+        <v>58</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Drill</t>
+          <t>58 to Edge and drill</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>30026196225</t>
+          <t>30061891516</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18 Oak 662x854 CAD-261962</t>
+          <t>18 Wte 415x947 CAD-618915</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Edge and drill</t>
+          <t>59 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>30061891516</t>
+          <t>30099999999</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18 Wte 415x947 CAD-618915</t>
+          <t>Tiled Panel (unknown SKU test row)</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Cut, edge and drill</t>
+          <t>1 to SKU NOT FOUND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>30099999999</t>
+          <t>30094410887</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tiled Panel (unknown SKU test row)</t>
+          <t>18 Oak 408x960 CAD-944108</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SKU NOT FOUND</t>
+          <t>100 to Edge and drill</t>
         </is>
       </c>
     </row>

--- a/sample/expected-output-mixed.xlsx
+++ b/sample/expected-output-mixed.xlsx
@@ -514,7 +514,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1 to SKU NOT FOUND</t>
+          <t>SKU NOT FOUND</t>
         </is>
       </c>
     </row>

--- a/sample/expected-output-mixed.xlsx
+++ b/sample/expected-output-mixed.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -429,11 +429,6 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>qty</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
           <t>actions</t>
         </is>
       </c>
@@ -449,10 +444,7 @@
           <t>18 Anth 651x824 CAD-409951</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>117</v>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>117 to Drill</t>
         </is>
@@ -469,10 +461,7 @@
           <t>18 Oak 662x854 CAD-261962</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>58</v>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>58 to Edge and drill</t>
         </is>
@@ -489,10 +478,7 @@
           <t>18 Wte 415x947 CAD-618915</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>59</v>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>59 to Cut, edge and drill</t>
         </is>
@@ -509,10 +495,7 @@
           <t>Tiled Panel (unknown SKU test row)</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>SKU NOT FOUND</t>
         </is>
@@ -529,10 +512,7 @@
           <t>18 Oak 408x960 CAD-944108</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>100</v>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>100 to Edge and drill</t>
         </is>

--- a/sample/expected-output-mixed.xlsx
+++ b/sample/expected-output-mixed.xlsx
@@ -34,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +42,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,104 +422,109 @@
   </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>sku</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>actions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>30040995108</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>18 Anth 651x824 CAD-409951</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="1" t="inlineStr">
         <is>
           <t>117 to Drill</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>30026196225</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>18 Oak 662x854 CAD-261962</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>58 to Edge and drill</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>30061891516</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>18 Wte 415x947 CAD-618915</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="1" t="inlineStr">
         <is>
           <t>59 to Cut, edge and drill</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>30099999999</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="1" t="inlineStr">
         <is>
           <t>Tiled Panel (unknown SKU test row)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>SKU NOT FOUND</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>30094410887</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t>18 Oak 408x960 CAD-944108</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="1" t="inlineStr">
         <is>
           <t>100 to Edge and drill</t>
         </is>
